--- a/mode_docx_gen/pmi_dzt/dtz2_modes/ДТЗ_2.xlsx
+++ b/mode_docx_gen/pmi_dzt/dtz2_modes/ДТЗ_2.xlsx
@@ -992,16 +992,16 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1052,13 +1052,13 @@
         <v>10.5</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="Z2" s="2" t="n">
         <v>1</v>
@@ -1070,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>5</v>
@@ -1399,31 +1399,31 @@
         <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>0.165</v>
+        <v>1.1</v>
       </c>
       <c r="R2" s="2" t="n">
         <v>240</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>0.165</v>
+        <v>1.1</v>
       </c>
       <c r="T2" s="2" t="n">
         <v>120</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>0.275</v>
+        <v>0.46</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.275</v>
+        <v>0.46</v>
       </c>
       <c r="X2" s="2" t="n">
         <v>240</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>0.275</v>
+        <v>0.46</v>
       </c>
       <c r="Z2" s="2" t="n">
         <v>120</v>
